--- a/L2++（DAN点检+电器下线）工程编排变化工时检讨（作业组合票）.xlsx
+++ b/L2++（DAN点检+电器下线）工程编排变化工时检讨（作业组合票）.xlsx
@@ -3,19 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10720"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F577FC2-8A22-2242-88D3-48245D76C589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6DA858-9776-F24C-83B2-3B297900088D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="9420" windowWidth="30240" windowHeight="9480" tabRatio="264" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" tabRatio="264" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作业组合票&amp;连续投入验证" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="19">
   <si>
     <t>L2++</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,12 +89,16 @@
     <t>›</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>ﬁ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +128,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -270,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -309,6 +321,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1655,6 +1670,277 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>673100</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="矩形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C9BD3CC-98AE-8E86-611E-3FB8C9F75B9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6451600" y="2057400"/>
+          <a:ext cx="1041400" cy="609600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="2000"/>
+            <a:t>L2++</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="2000"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="矩形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01646A2E-739D-A346-9F52-53ECE3DAA6D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7874000" y="2044700"/>
+          <a:ext cx="2159000" cy="609600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400"/>
+            <a:t>电检准备、电检</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="矩形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17C98F58-FA69-5C41-AB88-42A2BC4FB595}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10325100" y="2057400"/>
+          <a:ext cx="2159000" cy="609600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400"/>
+            <a:t>电检</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400"/>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400"/>
+            <a:t>、电检结束</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="矩形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27F4B51A-3D08-5740-9C73-18131E1BE619}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12712700" y="2044700"/>
+          <a:ext cx="2159000" cy="609600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400"/>
+            <a:t>电检</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400"/>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400"/>
+            <a:t>、电检结束</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -9907,7 +10193,9 @@
       <c r="NV20" s="3"/>
       <c r="NW20" s="3"/>
       <c r="NX20" s="3"/>
-      <c r="NY20" s="3"/>
+      <c r="NY20" s="14" t="s">
+        <v>18</v>
+      </c>
       <c r="NZ20" s="3"/>
       <c r="OA20" s="3"/>
       <c r="OB20" s="3"/>
@@ -10779,4 +11067,15 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B63537-E189-2749-98D4-F4064D855E52}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/L2++（DAN点检+电器下线）工程编排变化工时检讨（作业组合票）.xlsx
+++ b/L2++（DAN点检+电器下线）工程编排变化工时检讨（作业组合票）.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10720"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6DA858-9776-F24C-83B2-3B297900088D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0BB37D-39ED-1348-94A1-467E22FAE3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" tabRatio="264" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7740" yWindow="760" windowWidth="22340" windowHeight="17040" tabRatio="264" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作业组合票&amp;连续投入验证" sheetId="4" r:id="rId1"/>
@@ -305,6 +305,9 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -321,9 +324,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -550,15 +550,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>340</xdr:col>
-      <xdr:colOff>55228</xdr:colOff>
+      <xdr:colOff>42528</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>66434</xdr:rowOff>
+      <xdr:rowOff>104534</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>384</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:colOff>82550</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>81643</xdr:rowOff>
+      <xdr:rowOff>119743</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -573,8 +573,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="42441478" y="3264113"/>
-          <a:ext cx="5428451" cy="164887"/>
+          <a:off x="45610128" y="3698634"/>
+          <a:ext cx="5628022" cy="193009"/>
         </a:xfrm>
         <a:prstGeom prst="curvedConnector3">
           <a:avLst/>
@@ -2240,870 +2240,870 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1986" ht="45" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="9"/>
-      <c r="AG1" s="9"/>
-      <c r="AH1" s="9"/>
-      <c r="AI1" s="9"/>
-      <c r="AJ1" s="9"/>
-      <c r="AK1" s="9"/>
-      <c r="AL1" s="9"/>
-      <c r="AM1" s="9"/>
-      <c r="AN1" s="9"/>
-      <c r="AO1" s="9"/>
-      <c r="AP1" s="9"/>
-      <c r="AQ1" s="9"/>
-      <c r="AR1" s="9"/>
-      <c r="AS1" s="9"/>
-      <c r="AT1" s="9"/>
-      <c r="AU1" s="9"/>
-      <c r="AV1" s="9"/>
-      <c r="AW1" s="9"/>
-      <c r="AX1" s="9"/>
-      <c r="AY1" s="9"/>
-      <c r="AZ1" s="9"/>
-      <c r="BA1" s="9"/>
-      <c r="BB1" s="9"/>
-      <c r="BC1" s="9"/>
-      <c r="BD1" s="9"/>
-      <c r="BE1" s="9"/>
-      <c r="BF1" s="9"/>
-      <c r="BG1" s="9"/>
-      <c r="BH1" s="9"/>
-      <c r="BI1" s="9"/>
-      <c r="BJ1" s="9"/>
-      <c r="BK1" s="9"/>
-      <c r="BL1" s="9"/>
-      <c r="BM1" s="9"/>
-      <c r="BN1" s="9"/>
-      <c r="BO1" s="9"/>
-      <c r="BP1" s="9"/>
-      <c r="BQ1" s="9"/>
-      <c r="BR1" s="9"/>
-      <c r="BS1" s="9"/>
-      <c r="BT1" s="9"/>
-      <c r="BU1" s="9"/>
-      <c r="BV1" s="9"/>
-      <c r="BW1" s="9"/>
-      <c r="BX1" s="9"/>
-      <c r="BY1" s="9"/>
-      <c r="BZ1" s="9"/>
-      <c r="CA1" s="9"/>
-      <c r="CB1" s="9"/>
-      <c r="CC1" s="9"/>
-      <c r="CD1" s="9"/>
-      <c r="CE1" s="9"/>
-      <c r="CF1" s="9"/>
-      <c r="CG1" s="9"/>
-      <c r="CH1" s="9"/>
-      <c r="CI1" s="9"/>
-      <c r="CJ1" s="9"/>
-      <c r="CK1" s="9"/>
-      <c r="CL1" s="9"/>
-      <c r="CM1" s="9"/>
-      <c r="CN1" s="9"/>
-      <c r="CO1" s="9"/>
-      <c r="CP1" s="9"/>
-      <c r="CQ1" s="9"/>
-      <c r="CR1" s="9"/>
-      <c r="CS1" s="9"/>
-      <c r="CT1" s="9"/>
-      <c r="CU1" s="9"/>
-      <c r="CV1" s="9"/>
-      <c r="CW1" s="9"/>
-      <c r="CX1" s="9"/>
-      <c r="CY1" s="9"/>
-      <c r="CZ1" s="9"/>
-      <c r="DA1" s="9"/>
-      <c r="DB1" s="9"/>
-      <c r="DC1" s="9"/>
-      <c r="DD1" s="9"/>
-      <c r="DE1" s="9"/>
-      <c r="DF1" s="9"/>
-      <c r="DG1" s="9"/>
-      <c r="DH1" s="9"/>
-      <c r="DI1" s="9"/>
-      <c r="DJ1" s="9"/>
-      <c r="DK1" s="9"/>
-      <c r="DL1" s="9"/>
-      <c r="DM1" s="9"/>
-      <c r="DN1" s="9"/>
-      <c r="DO1" s="9"/>
-      <c r="DP1" s="9"/>
-      <c r="DQ1" s="9"/>
-      <c r="DR1" s="9"/>
-      <c r="DS1" s="9"/>
-      <c r="DT1" s="9"/>
-      <c r="DU1" s="9"/>
-      <c r="DV1" s="9"/>
-      <c r="DW1" s="9"/>
-      <c r="DX1" s="9"/>
-      <c r="DY1" s="9"/>
-      <c r="DZ1" s="9"/>
-      <c r="EA1" s="9"/>
-      <c r="EB1" s="9"/>
-      <c r="EC1" s="9"/>
-      <c r="ED1" s="9"/>
-      <c r="EE1" s="9"/>
-      <c r="EF1" s="9"/>
-      <c r="EG1" s="9"/>
-      <c r="EH1" s="9"/>
-      <c r="EI1" s="9"/>
-      <c r="EJ1" s="9"/>
-      <c r="EK1" s="9"/>
-      <c r="EL1" s="9"/>
-      <c r="EM1" s="9"/>
-      <c r="EN1" s="9"/>
-      <c r="EO1" s="9"/>
-      <c r="EP1" s="9"/>
-      <c r="EQ1" s="9"/>
-      <c r="ER1" s="9"/>
-      <c r="ES1" s="9"/>
-      <c r="ET1" s="9"/>
-      <c r="EU1" s="9"/>
-      <c r="EV1" s="9"/>
-      <c r="EW1" s="9"/>
-      <c r="EX1" s="9"/>
-      <c r="EY1" s="9"/>
-      <c r="EZ1" s="9"/>
-      <c r="FA1" s="9"/>
-      <c r="FB1" s="9"/>
-      <c r="FC1" s="9"/>
-      <c r="FD1" s="9"/>
-      <c r="FE1" s="9"/>
-      <c r="FF1" s="9"/>
-      <c r="FG1" s="9"/>
-      <c r="FH1" s="9"/>
-      <c r="FI1" s="9"/>
-      <c r="FJ1" s="9"/>
-      <c r="FK1" s="9"/>
-      <c r="FL1" s="9"/>
-      <c r="FM1" s="9"/>
-      <c r="FN1" s="9"/>
-      <c r="FO1" s="9"/>
-      <c r="FP1" s="9"/>
-      <c r="FQ1" s="9"/>
-      <c r="FR1" s="9"/>
-      <c r="FS1" s="9"/>
-      <c r="FT1" s="9"/>
-      <c r="FU1" s="9"/>
-      <c r="FV1" s="9"/>
-      <c r="FW1" s="9"/>
-      <c r="FX1" s="9"/>
-      <c r="FY1" s="9"/>
-      <c r="FZ1" s="9"/>
-      <c r="GA1" s="9"/>
-      <c r="GB1" s="9"/>
-      <c r="GC1" s="9"/>
-      <c r="GD1" s="9"/>
-      <c r="GE1" s="9"/>
-      <c r="GF1" s="9"/>
-      <c r="GG1" s="9"/>
-      <c r="GH1" s="9"/>
-      <c r="GI1" s="9"/>
-      <c r="GJ1" s="9"/>
-      <c r="GK1" s="9"/>
-      <c r="GL1" s="9"/>
-      <c r="GM1" s="9"/>
-      <c r="GN1" s="9"/>
-      <c r="GO1" s="9"/>
-      <c r="GP1" s="9"/>
-      <c r="GQ1" s="9"/>
-      <c r="GR1" s="9"/>
-      <c r="GS1" s="9"/>
-      <c r="GT1" s="9"/>
-      <c r="GU1" s="9"/>
-      <c r="GV1" s="9"/>
-      <c r="GW1" s="9"/>
-      <c r="GX1" s="9"/>
-      <c r="GY1" s="9"/>
-      <c r="GZ1" s="9"/>
-      <c r="HA1" s="9"/>
-      <c r="HB1" s="9"/>
-      <c r="HC1" s="9"/>
-      <c r="HD1" s="9"/>
-      <c r="HE1" s="9"/>
-      <c r="HF1" s="9"/>
-      <c r="HG1" s="9"/>
-      <c r="HH1" s="9"/>
-      <c r="HI1" s="9"/>
-      <c r="HJ1" s="9"/>
-      <c r="HK1" s="9"/>
-      <c r="HL1" s="9"/>
-      <c r="HM1" s="9"/>
-      <c r="HN1" s="9"/>
-      <c r="HO1" s="9"/>
-      <c r="HP1" s="9"/>
-      <c r="HQ1" s="9"/>
-      <c r="HR1" s="9"/>
-      <c r="HS1" s="9"/>
-      <c r="HT1" s="9"/>
-      <c r="HU1" s="9"/>
-      <c r="HV1" s="9"/>
-      <c r="HW1" s="9"/>
-      <c r="HX1" s="9"/>
-      <c r="HY1" s="9"/>
-      <c r="HZ1" s="9"/>
-      <c r="IA1" s="9"/>
-      <c r="IB1" s="9"/>
-      <c r="IC1" s="9"/>
-      <c r="ID1" s="9"/>
-      <c r="IE1" s="9"/>
-      <c r="IF1" s="9"/>
-      <c r="IG1" s="9"/>
-      <c r="IH1" s="9"/>
-      <c r="II1" s="9"/>
-      <c r="IJ1" s="9"/>
-      <c r="IK1" s="9"/>
-      <c r="IL1" s="9"/>
-      <c r="IM1" s="9"/>
-      <c r="IN1" s="9"/>
-      <c r="IO1" s="9"/>
-      <c r="IP1" s="9"/>
-      <c r="IQ1" s="9"/>
-      <c r="IR1" s="9"/>
-      <c r="IS1" s="9"/>
-      <c r="IT1" s="9"/>
-      <c r="IU1" s="9"/>
-      <c r="IV1" s="9"/>
-      <c r="IW1" s="9"/>
-      <c r="IX1" s="9"/>
-      <c r="IY1" s="9"/>
-      <c r="IZ1" s="9"/>
-      <c r="JA1" s="9"/>
-      <c r="JB1" s="9"/>
-      <c r="JC1" s="9"/>
-      <c r="JD1" s="9"/>
-      <c r="JE1" s="9"/>
-      <c r="JF1" s="9"/>
-      <c r="JG1" s="9"/>
-      <c r="JH1" s="9"/>
-      <c r="JI1" s="9"/>
-      <c r="JJ1" s="9"/>
-      <c r="JK1" s="9"/>
-      <c r="JL1" s="9"/>
-      <c r="JM1" s="9"/>
-      <c r="JN1" s="9"/>
-      <c r="JO1" s="9"/>
-      <c r="JP1" s="9"/>
-      <c r="JQ1" s="9"/>
-      <c r="JR1" s="9"/>
-      <c r="JS1" s="9"/>
-      <c r="JT1" s="9"/>
-      <c r="JU1" s="9"/>
-      <c r="JV1" s="9"/>
-      <c r="JW1" s="9"/>
-      <c r="JX1" s="9"/>
-      <c r="JY1" s="9"/>
-      <c r="JZ1" s="9"/>
-      <c r="KA1" s="9"/>
-      <c r="KB1" s="9"/>
-      <c r="KC1" s="9"/>
-      <c r="KD1" s="9"/>
-      <c r="KE1" s="9"/>
-      <c r="KF1" s="9"/>
-      <c r="KG1" s="9"/>
-      <c r="KH1" s="9"/>
-      <c r="KI1" s="9"/>
-      <c r="KJ1" s="9"/>
-      <c r="KK1" s="9"/>
-      <c r="KL1" s="9"/>
-      <c r="KM1" s="9"/>
-      <c r="KN1" s="9"/>
-      <c r="KO1" s="9"/>
-      <c r="KP1" s="9"/>
-      <c r="KQ1" s="9"/>
-      <c r="KR1" s="9"/>
-      <c r="KS1" s="9"/>
-      <c r="KT1" s="9"/>
-      <c r="KU1" s="9"/>
-      <c r="KV1" s="9"/>
-      <c r="KW1" s="9"/>
-      <c r="KX1" s="9"/>
-      <c r="KY1" s="9"/>
-      <c r="KZ1" s="9"/>
-      <c r="LA1" s="9"/>
-      <c r="LB1" s="9"/>
-      <c r="LC1" s="9"/>
-      <c r="LD1" s="9"/>
-      <c r="LE1" s="9"/>
-      <c r="LF1" s="9"/>
-      <c r="LG1" s="9"/>
-      <c r="LH1" s="9"/>
-      <c r="LI1" s="9"/>
-      <c r="LJ1" s="9"/>
-      <c r="LK1" s="9"/>
-      <c r="LL1" s="9"/>
-      <c r="LM1" s="9"/>
-      <c r="LN1" s="9"/>
-      <c r="LO1" s="9"/>
-      <c r="LP1" s="9"/>
-      <c r="LQ1" s="9"/>
-      <c r="LR1" s="9"/>
-      <c r="LS1" s="9"/>
-      <c r="LT1" s="9"/>
-      <c r="LU1" s="9"/>
-      <c r="LV1" s="9"/>
-      <c r="LW1" s="9"/>
-      <c r="LX1" s="9"/>
-      <c r="LY1" s="9"/>
-      <c r="LZ1" s="9"/>
-      <c r="MA1" s="9"/>
-      <c r="MB1" s="9"/>
-      <c r="MC1" s="9"/>
-      <c r="MD1" s="9"/>
-      <c r="ME1" s="9"/>
-      <c r="MF1" s="9"/>
-      <c r="MG1" s="9"/>
-      <c r="MH1" s="9"/>
-      <c r="MI1" s="9"/>
-      <c r="MJ1" s="9"/>
-      <c r="MK1" s="9"/>
-      <c r="ML1" s="9"/>
-      <c r="MM1" s="9"/>
-      <c r="MN1" s="9"/>
-      <c r="MO1" s="9"/>
-      <c r="MP1" s="9"/>
-      <c r="MQ1" s="9"/>
-      <c r="MR1" s="9"/>
-      <c r="MS1" s="9"/>
-      <c r="MT1" s="9"/>
-      <c r="MU1" s="9"/>
-      <c r="MV1" s="9"/>
-      <c r="MW1" s="9"/>
-      <c r="MX1" s="9"/>
-      <c r="MY1" s="9"/>
-      <c r="MZ1" s="9"/>
-      <c r="NA1" s="9"/>
-      <c r="NB1" s="9"/>
-      <c r="NC1" s="9"/>
-      <c r="ND1" s="9"/>
-      <c r="NE1" s="9"/>
-      <c r="NF1" s="9"/>
-      <c r="NG1" s="9"/>
-      <c r="NH1" s="9"/>
-      <c r="NI1" s="9"/>
-      <c r="NJ1" s="9"/>
-      <c r="NK1" s="9"/>
-      <c r="NL1" s="9"/>
-      <c r="NM1" s="9"/>
-      <c r="NN1" s="9"/>
-      <c r="NO1" s="9"/>
-      <c r="NP1" s="9"/>
-      <c r="NQ1" s="9"/>
-      <c r="NR1" s="9"/>
-      <c r="NS1" s="9"/>
-      <c r="NT1" s="9"/>
-      <c r="NU1" s="9"/>
-      <c r="NV1" s="9"/>
-      <c r="NW1" s="9"/>
-      <c r="NX1" s="9"/>
-      <c r="NY1" s="9"/>
-      <c r="NZ1" s="9"/>
-      <c r="OA1" s="9"/>
-      <c r="OB1" s="9"/>
-      <c r="OC1" s="9"/>
-      <c r="OD1" s="9"/>
-      <c r="OE1" s="9"/>
-      <c r="OF1" s="9"/>
-      <c r="OG1" s="9"/>
-      <c r="OH1" s="9"/>
-      <c r="OI1" s="9"/>
-      <c r="OJ1" s="9"/>
-      <c r="OK1" s="9"/>
-      <c r="OL1" s="9"/>
-      <c r="OM1" s="9"/>
-      <c r="ON1" s="9"/>
-      <c r="OO1" s="9"/>
-      <c r="OP1" s="9"/>
-      <c r="OQ1" s="9"/>
-      <c r="OR1" s="9"/>
-      <c r="OS1" s="9"/>
-      <c r="OT1" s="9"/>
-      <c r="OU1" s="9"/>
-      <c r="OV1" s="9"/>
-      <c r="OW1" s="9"/>
-      <c r="OX1" s="9"/>
-      <c r="OY1" s="9"/>
-      <c r="OZ1" s="9"/>
-      <c r="PA1" s="9"/>
-      <c r="PB1" s="9"/>
-      <c r="PC1" s="9"/>
-      <c r="PD1" s="9"/>
-      <c r="PE1" s="9"/>
-      <c r="PF1" s="9"/>
-      <c r="PG1" s="9"/>
-      <c r="PH1" s="9"/>
-      <c r="PI1" s="9"/>
-      <c r="PJ1" s="9"/>
-      <c r="PK1" s="9"/>
-      <c r="PL1" s="9"/>
-      <c r="PM1" s="9"/>
-      <c r="PN1" s="9"/>
-      <c r="PO1" s="9"/>
-      <c r="PP1" s="9"/>
-      <c r="PQ1" s="9"/>
-      <c r="PR1" s="9"/>
-      <c r="PS1" s="9"/>
-      <c r="PT1" s="9"/>
-      <c r="PU1" s="9"/>
-      <c r="PV1" s="9"/>
-      <c r="PW1" s="9"/>
-      <c r="PX1" s="9"/>
-      <c r="PY1" s="9"/>
-      <c r="PZ1" s="9"/>
-      <c r="QA1" s="9"/>
-      <c r="QB1" s="9"/>
-      <c r="QC1" s="9"/>
-      <c r="QD1" s="9"/>
-      <c r="QE1" s="9"/>
-      <c r="QF1" s="9"/>
-      <c r="QG1" s="9"/>
-      <c r="QH1" s="9"/>
-      <c r="QI1" s="9"/>
-      <c r="QJ1" s="9"/>
-      <c r="QK1" s="9"/>
-      <c r="QL1" s="9"/>
-      <c r="QM1" s="9"/>
-      <c r="QN1" s="9"/>
-      <c r="QO1" s="9"/>
-      <c r="QP1" s="9"/>
-      <c r="QQ1" s="9"/>
-      <c r="QR1" s="9"/>
-      <c r="QS1" s="9"/>
-      <c r="QT1" s="9"/>
-      <c r="QU1" s="9"/>
-      <c r="QV1" s="9"/>
-      <c r="QW1" s="9"/>
-      <c r="QX1" s="9"/>
-      <c r="QY1" s="9"/>
-      <c r="QZ1" s="9"/>
-      <c r="RA1" s="9"/>
-      <c r="RB1" s="9"/>
-      <c r="RC1" s="9"/>
-      <c r="RD1" s="9"/>
-      <c r="RE1" s="9"/>
-      <c r="RF1" s="9"/>
-      <c r="RG1" s="9"/>
-      <c r="RH1" s="9"/>
-      <c r="RI1" s="9"/>
-      <c r="RJ1" s="9"/>
-      <c r="RK1" s="9"/>
-      <c r="RL1" s="9"/>
-      <c r="RM1" s="9"/>
-      <c r="RN1" s="9"/>
-      <c r="RO1" s="9"/>
-      <c r="RP1" s="9"/>
-      <c r="RQ1" s="9"/>
-      <c r="RR1" s="9"/>
-      <c r="RS1" s="9"/>
-      <c r="RT1" s="9"/>
-      <c r="RU1" s="9"/>
-      <c r="RV1" s="9"/>
-      <c r="RW1" s="9"/>
-      <c r="RX1" s="9"/>
-      <c r="RY1" s="9"/>
-      <c r="RZ1" s="9"/>
-      <c r="SA1" s="9"/>
-      <c r="SB1" s="9"/>
-      <c r="SC1" s="9"/>
-      <c r="SD1" s="9"/>
-      <c r="SE1" s="9"/>
-      <c r="SF1" s="9"/>
-      <c r="SG1" s="9"/>
-      <c r="SH1" s="9"/>
-      <c r="SI1" s="9"/>
-      <c r="SJ1" s="9"/>
-      <c r="SK1" s="9"/>
-      <c r="SL1" s="9"/>
-      <c r="SM1" s="9"/>
-      <c r="SN1" s="9"/>
-      <c r="SO1" s="9"/>
-      <c r="SP1" s="9"/>
-      <c r="SQ1" s="9"/>
-      <c r="SR1" s="9"/>
-      <c r="SS1" s="9"/>
-      <c r="ST1" s="9"/>
-      <c r="SU1" s="9"/>
-      <c r="SV1" s="9"/>
-      <c r="SW1" s="9"/>
-      <c r="SX1" s="9"/>
-      <c r="SY1" s="9"/>
-      <c r="SZ1" s="9"/>
-      <c r="TA1" s="9"/>
-      <c r="TB1" s="9"/>
-      <c r="TC1" s="9"/>
-      <c r="TD1" s="9"/>
-      <c r="TE1" s="9"/>
-      <c r="TF1" s="9"/>
-      <c r="TG1" s="9"/>
-      <c r="TH1" s="9"/>
-      <c r="TI1" s="9"/>
-      <c r="TJ1" s="9"/>
-      <c r="TK1" s="9"/>
-      <c r="TL1" s="9"/>
-      <c r="TM1" s="9"/>
-      <c r="TN1" s="9"/>
-      <c r="TO1" s="9"/>
-      <c r="TP1" s="9"/>
-      <c r="TQ1" s="9"/>
-      <c r="TR1" s="9"/>
-      <c r="TS1" s="9"/>
-      <c r="TT1" s="9"/>
-      <c r="TU1" s="9"/>
-      <c r="TV1" s="9"/>
-      <c r="TW1" s="9"/>
-      <c r="TX1" s="9"/>
-      <c r="TY1" s="9"/>
-      <c r="TZ1" s="9"/>
-      <c r="UA1" s="9"/>
-      <c r="UB1" s="9"/>
-      <c r="UC1" s="9"/>
-      <c r="UD1" s="9"/>
-      <c r="UE1" s="9"/>
-      <c r="UF1" s="9"/>
-      <c r="UG1" s="9"/>
-      <c r="UH1" s="9"/>
-      <c r="UI1" s="9"/>
-      <c r="UJ1" s="9"/>
-      <c r="UK1" s="9"/>
-      <c r="UL1" s="9"/>
-      <c r="UM1" s="9"/>
-      <c r="UN1" s="9"/>
-      <c r="UO1" s="9"/>
-      <c r="UP1" s="9"/>
-      <c r="UQ1" s="9"/>
-      <c r="UR1" s="9"/>
-      <c r="US1" s="9"/>
-      <c r="UT1" s="9"/>
-      <c r="UU1" s="9"/>
-      <c r="UV1" s="9"/>
-      <c r="UW1" s="9"/>
-      <c r="UX1" s="9"/>
-      <c r="UY1" s="9"/>
-      <c r="UZ1" s="9"/>
-      <c r="VA1" s="9"/>
-      <c r="VB1" s="9"/>
-      <c r="VC1" s="9"/>
-      <c r="VD1" s="9"/>
-      <c r="VE1" s="9"/>
-      <c r="VF1" s="9"/>
-      <c r="VG1" s="9"/>
-      <c r="VH1" s="9"/>
-      <c r="VI1" s="9"/>
-      <c r="VJ1" s="9"/>
-      <c r="VK1" s="9"/>
-      <c r="VL1" s="9"/>
-      <c r="VM1" s="9"/>
-      <c r="VN1" s="9"/>
-      <c r="VO1" s="9"/>
-      <c r="VP1" s="9"/>
-      <c r="VQ1" s="9"/>
-      <c r="VR1" s="9"/>
-      <c r="VS1" s="9"/>
-      <c r="VT1" s="9"/>
-      <c r="VU1" s="9"/>
-      <c r="VV1" s="9"/>
-      <c r="VW1" s="9"/>
-      <c r="VX1" s="9"/>
-      <c r="VY1" s="9"/>
-      <c r="VZ1" s="9"/>
-      <c r="WA1" s="9"/>
-      <c r="WB1" s="9"/>
-      <c r="WC1" s="9"/>
-      <c r="WD1" s="9"/>
-      <c r="WE1" s="9"/>
-      <c r="WF1" s="9"/>
-      <c r="WG1" s="9"/>
-      <c r="WH1" s="9"/>
-      <c r="WI1" s="9"/>
-      <c r="WJ1" s="9"/>
-      <c r="WK1" s="9"/>
-      <c r="WL1" s="9"/>
-      <c r="WM1" s="9"/>
-      <c r="WN1" s="9"/>
-      <c r="WO1" s="9"/>
-      <c r="WP1" s="9"/>
-      <c r="WQ1" s="9"/>
-      <c r="WR1" s="9"/>
-      <c r="WS1" s="9"/>
-      <c r="WT1" s="9"/>
-      <c r="WU1" s="9"/>
-      <c r="WV1" s="9"/>
-      <c r="WW1" s="9"/>
-      <c r="WX1" s="9"/>
-      <c r="WY1" s="9"/>
-      <c r="WZ1" s="9"/>
-      <c r="XA1" s="9"/>
-      <c r="XB1" s="9"/>
-      <c r="XC1" s="9"/>
-      <c r="XD1" s="9"/>
-      <c r="XE1" s="9"/>
-      <c r="XF1" s="9"/>
-      <c r="XG1" s="9"/>
-      <c r="XH1" s="9"/>
-      <c r="XI1" s="9"/>
-      <c r="XJ1" s="9"/>
-      <c r="XK1" s="9"/>
-      <c r="XL1" s="9"/>
-      <c r="XM1" s="9"/>
-      <c r="XN1" s="9"/>
-      <c r="XO1" s="9"/>
-      <c r="XP1" s="9"/>
-      <c r="XQ1" s="9"/>
-      <c r="XR1" s="9"/>
-      <c r="XS1" s="9"/>
-      <c r="XT1" s="9"/>
-      <c r="XU1" s="9"/>
-      <c r="XV1" s="9"/>
-      <c r="XW1" s="9"/>
-      <c r="XX1" s="9"/>
-      <c r="XY1" s="9"/>
-      <c r="XZ1" s="9"/>
-      <c r="YA1" s="9"/>
-      <c r="YB1" s="9"/>
-      <c r="YC1" s="9"/>
-      <c r="YD1" s="9"/>
-      <c r="YE1" s="9"/>
-      <c r="YF1" s="9"/>
-      <c r="YG1" s="9"/>
-      <c r="YH1" s="9"/>
-      <c r="YI1" s="9"/>
-      <c r="YJ1" s="9"/>
-      <c r="YK1" s="9"/>
-      <c r="YL1" s="9"/>
-      <c r="YM1" s="9"/>
-      <c r="YN1" s="9"/>
-      <c r="YO1" s="9"/>
-      <c r="YP1" s="9"/>
-      <c r="YQ1" s="9"/>
-      <c r="YR1" s="9"/>
-      <c r="YS1" s="9"/>
-      <c r="YT1" s="9"/>
-      <c r="YU1" s="9"/>
-      <c r="YV1" s="9"/>
-      <c r="YW1" s="9"/>
-      <c r="YX1" s="9"/>
-      <c r="YY1" s="9"/>
-      <c r="YZ1" s="9"/>
-      <c r="ZA1" s="9"/>
-      <c r="ZB1" s="9"/>
-      <c r="ZC1" s="9"/>
-      <c r="ZD1" s="9"/>
-      <c r="ZE1" s="9"/>
-      <c r="ZF1" s="9"/>
-      <c r="ZG1" s="9"/>
-      <c r="ZH1" s="9"/>
-      <c r="ZI1" s="9"/>
-      <c r="ZJ1" s="9"/>
-      <c r="ZK1" s="9"/>
-      <c r="ZL1" s="9"/>
-      <c r="ZM1" s="9"/>
-      <c r="ZN1" s="9"/>
-      <c r="ZO1" s="9"/>
-      <c r="ZP1" s="9"/>
-      <c r="ZQ1" s="9"/>
-      <c r="ZR1" s="9"/>
-      <c r="ZS1" s="9"/>
-      <c r="ZT1" s="9"/>
-      <c r="ZU1" s="9"/>
-      <c r="ZV1" s="9"/>
-      <c r="ZW1" s="9"/>
-      <c r="ZX1" s="9"/>
-      <c r="ZY1" s="9"/>
-      <c r="ZZ1" s="9"/>
-      <c r="AAA1" s="9"/>
-      <c r="AAB1" s="9"/>
-      <c r="AAC1" s="9"/>
-      <c r="AAD1" s="9"/>
-      <c r="AAE1" s="9"/>
-      <c r="AAF1" s="9"/>
-      <c r="AAG1" s="9"/>
-      <c r="AAH1" s="9"/>
-      <c r="AAI1" s="9"/>
-      <c r="AAJ1" s="9"/>
-      <c r="AAK1" s="9"/>
-      <c r="AAL1" s="9"/>
-      <c r="AAM1" s="9"/>
-      <c r="AAN1" s="9"/>
-      <c r="AAO1" s="9"/>
-      <c r="AAP1" s="9"/>
-      <c r="AAQ1" s="9"/>
-      <c r="AAR1" s="9"/>
-      <c r="AAS1" s="9"/>
-      <c r="AAT1" s="9"/>
-      <c r="AAU1" s="9"/>
-      <c r="AAV1" s="9"/>
-      <c r="AAW1" s="9"/>
-      <c r="AAX1" s="9"/>
-      <c r="AAY1" s="9"/>
-      <c r="AAZ1" s="9"/>
-      <c r="ABA1" s="9"/>
-      <c r="ABB1" s="9"/>
-      <c r="ABC1" s="9"/>
-      <c r="ABD1" s="9"/>
-      <c r="ABE1" s="9"/>
-      <c r="ABF1" s="9"/>
-      <c r="ABG1" s="9"/>
-      <c r="ABH1" s="9"/>
-      <c r="ABI1" s="9"/>
-      <c r="ABJ1" s="9"/>
-      <c r="ABK1" s="9"/>
-      <c r="ABL1" s="9"/>
-      <c r="ABM1" s="9"/>
-      <c r="ABN1" s="9"/>
-      <c r="ABO1" s="9"/>
-      <c r="ABP1" s="9"/>
-      <c r="ABQ1" s="9"/>
-      <c r="ABR1" s="9"/>
-      <c r="ABS1" s="9"/>
-      <c r="ABT1" s="9"/>
-      <c r="ABU1" s="9"/>
-      <c r="ABV1" s="9"/>
-      <c r="ABW1" s="9"/>
-      <c r="ABX1" s="9"/>
-      <c r="ABY1" s="9"/>
-      <c r="ABZ1" s="9"/>
-      <c r="ACA1" s="9"/>
-      <c r="ACB1" s="9"/>
-      <c r="ACC1" s="9"/>
-      <c r="ACD1" s="9"/>
-      <c r="ACE1" s="9"/>
-      <c r="ACF1" s="9"/>
-      <c r="ACG1" s="9"/>
-      <c r="ACH1" s="9"/>
-      <c r="ACI1" s="9"/>
-      <c r="ACJ1" s="9"/>
-      <c r="ACK1" s="9"/>
-      <c r="ACL1" s="9"/>
-      <c r="ACM1" s="9"/>
-      <c r="ACN1" s="9"/>
-      <c r="ACO1" s="9"/>
-      <c r="ACP1" s="9"/>
-      <c r="ACQ1" s="9"/>
-      <c r="ACR1" s="9"/>
-      <c r="ACS1" s="9"/>
-      <c r="ACT1" s="9"/>
-      <c r="ACU1" s="9"/>
-      <c r="ACV1" s="9"/>
-      <c r="ACW1" s="9"/>
-      <c r="ACX1" s="9"/>
-      <c r="ACY1" s="9"/>
-      <c r="ACZ1" s="9"/>
-      <c r="ADA1" s="9"/>
-      <c r="ADB1" s="9"/>
-      <c r="ADC1" s="9"/>
-      <c r="ADD1" s="9"/>
-      <c r="ADE1" s="9"/>
-      <c r="ADF1" s="9"/>
-      <c r="ADG1" s="9"/>
-      <c r="ADH1" s="9"/>
-      <c r="ADI1" s="9"/>
-      <c r="ADJ1" s="9"/>
-      <c r="ADK1" s="9"/>
-      <c r="ADL1" s="9"/>
-      <c r="ADM1" s="9"/>
-      <c r="ADN1" s="9"/>
-      <c r="ADO1" s="9"/>
-      <c r="ADP1" s="9"/>
-      <c r="ADQ1" s="9"/>
-      <c r="ADR1" s="9"/>
-      <c r="ADS1" s="9"/>
-      <c r="ADT1" s="9"/>
-      <c r="ADU1" s="9"/>
-      <c r="ADV1" s="9"/>
-      <c r="ADW1" s="9"/>
-      <c r="ADX1" s="9"/>
-      <c r="ADY1" s="9"/>
-      <c r="ADZ1" s="9"/>
-      <c r="AEA1" s="9"/>
-      <c r="AEB1" s="9"/>
-      <c r="AEC1" s="9"/>
-      <c r="AED1" s="9"/>
-      <c r="AEE1" s="9"/>
-      <c r="AEF1" s="9"/>
-      <c r="AEG1" s="9"/>
-      <c r="AEH1" s="9"/>
-      <c r="AEI1" s="9"/>
-      <c r="AEJ1" s="9"/>
-      <c r="AEK1" s="9"/>
-      <c r="AEL1" s="9"/>
-      <c r="AEM1" s="9"/>
-      <c r="AEN1" s="9"/>
-      <c r="AEO1" s="9"/>
-      <c r="AEP1" s="9"/>
-      <c r="AEQ1" s="9"/>
-      <c r="AER1" s="9"/>
-      <c r="AES1" s="9"/>
-      <c r="AET1" s="9"/>
-      <c r="AEU1" s="9"/>
-      <c r="AEV1" s="9"/>
-      <c r="AEW1" s="9"/>
-      <c r="AEX1" s="9"/>
-      <c r="AEY1" s="9"/>
-      <c r="AEZ1" s="9"/>
-      <c r="AFA1" s="9"/>
-      <c r="AFB1" s="9"/>
-      <c r="AFC1" s="9"/>
-      <c r="AFD1" s="9"/>
-      <c r="AFE1" s="9"/>
-      <c r="AFF1" s="9"/>
-      <c r="AFG1" s="9"/>
-      <c r="AFH1" s="9"/>
-      <c r="AFI1" s="9"/>
-      <c r="AFJ1" s="9"/>
-      <c r="AFK1" s="9"/>
-      <c r="AFL1" s="9"/>
-      <c r="AFM1" s="9"/>
-      <c r="AFN1" s="9"/>
-      <c r="AFO1" s="9"/>
-      <c r="AFP1" s="9"/>
-      <c r="AFQ1" s="9"/>
-      <c r="AFR1" s="9"/>
-      <c r="AFS1" s="9"/>
-      <c r="AFT1" s="9"/>
-      <c r="AFU1" s="9"/>
-      <c r="AFV1" s="9"/>
-      <c r="AFW1" s="9"/>
-      <c r="AFX1" s="9"/>
-      <c r="AFY1" s="9"/>
-      <c r="AFZ1" s="9"/>
-      <c r="AGA1" s="9"/>
-      <c r="AGB1" s="9"/>
-      <c r="AGC1" s="9"/>
-      <c r="AGD1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="10"/>
+      <c r="AH1" s="10"/>
+      <c r="AI1" s="10"/>
+      <c r="AJ1" s="10"/>
+      <c r="AK1" s="10"/>
+      <c r="AL1" s="10"/>
+      <c r="AM1" s="10"/>
+      <c r="AN1" s="10"/>
+      <c r="AO1" s="10"/>
+      <c r="AP1" s="10"/>
+      <c r="AQ1" s="10"/>
+      <c r="AR1" s="10"/>
+      <c r="AS1" s="10"/>
+      <c r="AT1" s="10"/>
+      <c r="AU1" s="10"/>
+      <c r="AV1" s="10"/>
+      <c r="AW1" s="10"/>
+      <c r="AX1" s="10"/>
+      <c r="AY1" s="10"/>
+      <c r="AZ1" s="10"/>
+      <c r="BA1" s="10"/>
+      <c r="BB1" s="10"/>
+      <c r="BC1" s="10"/>
+      <c r="BD1" s="10"/>
+      <c r="BE1" s="10"/>
+      <c r="BF1" s="10"/>
+      <c r="BG1" s="10"/>
+      <c r="BH1" s="10"/>
+      <c r="BI1" s="10"/>
+      <c r="BJ1" s="10"/>
+      <c r="BK1" s="10"/>
+      <c r="BL1" s="10"/>
+      <c r="BM1" s="10"/>
+      <c r="BN1" s="10"/>
+      <c r="BO1" s="10"/>
+      <c r="BP1" s="10"/>
+      <c r="BQ1" s="10"/>
+      <c r="BR1" s="10"/>
+      <c r="BS1" s="10"/>
+      <c r="BT1" s="10"/>
+      <c r="BU1" s="10"/>
+      <c r="BV1" s="10"/>
+      <c r="BW1" s="10"/>
+      <c r="BX1" s="10"/>
+      <c r="BY1" s="10"/>
+      <c r="BZ1" s="10"/>
+      <c r="CA1" s="10"/>
+      <c r="CB1" s="10"/>
+      <c r="CC1" s="10"/>
+      <c r="CD1" s="10"/>
+      <c r="CE1" s="10"/>
+      <c r="CF1" s="10"/>
+      <c r="CG1" s="10"/>
+      <c r="CH1" s="10"/>
+      <c r="CI1" s="10"/>
+      <c r="CJ1" s="10"/>
+      <c r="CK1" s="10"/>
+      <c r="CL1" s="10"/>
+      <c r="CM1" s="10"/>
+      <c r="CN1" s="10"/>
+      <c r="CO1" s="10"/>
+      <c r="CP1" s="10"/>
+      <c r="CQ1" s="10"/>
+      <c r="CR1" s="10"/>
+      <c r="CS1" s="10"/>
+      <c r="CT1" s="10"/>
+      <c r="CU1" s="10"/>
+      <c r="CV1" s="10"/>
+      <c r="CW1" s="10"/>
+      <c r="CX1" s="10"/>
+      <c r="CY1" s="10"/>
+      <c r="CZ1" s="10"/>
+      <c r="DA1" s="10"/>
+      <c r="DB1" s="10"/>
+      <c r="DC1" s="10"/>
+      <c r="DD1" s="10"/>
+      <c r="DE1" s="10"/>
+      <c r="DF1" s="10"/>
+      <c r="DG1" s="10"/>
+      <c r="DH1" s="10"/>
+      <c r="DI1" s="10"/>
+      <c r="DJ1" s="10"/>
+      <c r="DK1" s="10"/>
+      <c r="DL1" s="10"/>
+      <c r="DM1" s="10"/>
+      <c r="DN1" s="10"/>
+      <c r="DO1" s="10"/>
+      <c r="DP1" s="10"/>
+      <c r="DQ1" s="10"/>
+      <c r="DR1" s="10"/>
+      <c r="DS1" s="10"/>
+      <c r="DT1" s="10"/>
+      <c r="DU1" s="10"/>
+      <c r="DV1" s="10"/>
+      <c r="DW1" s="10"/>
+      <c r="DX1" s="10"/>
+      <c r="DY1" s="10"/>
+      <c r="DZ1" s="10"/>
+      <c r="EA1" s="10"/>
+      <c r="EB1" s="10"/>
+      <c r="EC1" s="10"/>
+      <c r="ED1" s="10"/>
+      <c r="EE1" s="10"/>
+      <c r="EF1" s="10"/>
+      <c r="EG1" s="10"/>
+      <c r="EH1" s="10"/>
+      <c r="EI1" s="10"/>
+      <c r="EJ1" s="10"/>
+      <c r="EK1" s="10"/>
+      <c r="EL1" s="10"/>
+      <c r="EM1" s="10"/>
+      <c r="EN1" s="10"/>
+      <c r="EO1" s="10"/>
+      <c r="EP1" s="10"/>
+      <c r="EQ1" s="10"/>
+      <c r="ER1" s="10"/>
+      <c r="ES1" s="10"/>
+      <c r="ET1" s="10"/>
+      <c r="EU1" s="10"/>
+      <c r="EV1" s="10"/>
+      <c r="EW1" s="10"/>
+      <c r="EX1" s="10"/>
+      <c r="EY1" s="10"/>
+      <c r="EZ1" s="10"/>
+      <c r="FA1" s="10"/>
+      <c r="FB1" s="10"/>
+      <c r="FC1" s="10"/>
+      <c r="FD1" s="10"/>
+      <c r="FE1" s="10"/>
+      <c r="FF1" s="10"/>
+      <c r="FG1" s="10"/>
+      <c r="FH1" s="10"/>
+      <c r="FI1" s="10"/>
+      <c r="FJ1" s="10"/>
+      <c r="FK1" s="10"/>
+      <c r="FL1" s="10"/>
+      <c r="FM1" s="10"/>
+      <c r="FN1" s="10"/>
+      <c r="FO1" s="10"/>
+      <c r="FP1" s="10"/>
+      <c r="FQ1" s="10"/>
+      <c r="FR1" s="10"/>
+      <c r="FS1" s="10"/>
+      <c r="FT1" s="10"/>
+      <c r="FU1" s="10"/>
+      <c r="FV1" s="10"/>
+      <c r="FW1" s="10"/>
+      <c r="FX1" s="10"/>
+      <c r="FY1" s="10"/>
+      <c r="FZ1" s="10"/>
+      <c r="GA1" s="10"/>
+      <c r="GB1" s="10"/>
+      <c r="GC1" s="10"/>
+      <c r="GD1" s="10"/>
+      <c r="GE1" s="10"/>
+      <c r="GF1" s="10"/>
+      <c r="GG1" s="10"/>
+      <c r="GH1" s="10"/>
+      <c r="GI1" s="10"/>
+      <c r="GJ1" s="10"/>
+      <c r="GK1" s="10"/>
+      <c r="GL1" s="10"/>
+      <c r="GM1" s="10"/>
+      <c r="GN1" s="10"/>
+      <c r="GO1" s="10"/>
+      <c r="GP1" s="10"/>
+      <c r="GQ1" s="10"/>
+      <c r="GR1" s="10"/>
+      <c r="GS1" s="10"/>
+      <c r="GT1" s="10"/>
+      <c r="GU1" s="10"/>
+      <c r="GV1" s="10"/>
+      <c r="GW1" s="10"/>
+      <c r="GX1" s="10"/>
+      <c r="GY1" s="10"/>
+      <c r="GZ1" s="10"/>
+      <c r="HA1" s="10"/>
+      <c r="HB1" s="10"/>
+      <c r="HC1" s="10"/>
+      <c r="HD1" s="10"/>
+      <c r="HE1" s="10"/>
+      <c r="HF1" s="10"/>
+      <c r="HG1" s="10"/>
+      <c r="HH1" s="10"/>
+      <c r="HI1" s="10"/>
+      <c r="HJ1" s="10"/>
+      <c r="HK1" s="10"/>
+      <c r="HL1" s="10"/>
+      <c r="HM1" s="10"/>
+      <c r="HN1" s="10"/>
+      <c r="HO1" s="10"/>
+      <c r="HP1" s="10"/>
+      <c r="HQ1" s="10"/>
+      <c r="HR1" s="10"/>
+      <c r="HS1" s="10"/>
+      <c r="HT1" s="10"/>
+      <c r="HU1" s="10"/>
+      <c r="HV1" s="10"/>
+      <c r="HW1" s="10"/>
+      <c r="HX1" s="10"/>
+      <c r="HY1" s="10"/>
+      <c r="HZ1" s="10"/>
+      <c r="IA1" s="10"/>
+      <c r="IB1" s="10"/>
+      <c r="IC1" s="10"/>
+      <c r="ID1" s="10"/>
+      <c r="IE1" s="10"/>
+      <c r="IF1" s="10"/>
+      <c r="IG1" s="10"/>
+      <c r="IH1" s="10"/>
+      <c r="II1" s="10"/>
+      <c r="IJ1" s="10"/>
+      <c r="IK1" s="10"/>
+      <c r="IL1" s="10"/>
+      <c r="IM1" s="10"/>
+      <c r="IN1" s="10"/>
+      <c r="IO1" s="10"/>
+      <c r="IP1" s="10"/>
+      <c r="IQ1" s="10"/>
+      <c r="IR1" s="10"/>
+      <c r="IS1" s="10"/>
+      <c r="IT1" s="10"/>
+      <c r="IU1" s="10"/>
+      <c r="IV1" s="10"/>
+      <c r="IW1" s="10"/>
+      <c r="IX1" s="10"/>
+      <c r="IY1" s="10"/>
+      <c r="IZ1" s="10"/>
+      <c r="JA1" s="10"/>
+      <c r="JB1" s="10"/>
+      <c r="JC1" s="10"/>
+      <c r="JD1" s="10"/>
+      <c r="JE1" s="10"/>
+      <c r="JF1" s="10"/>
+      <c r="JG1" s="10"/>
+      <c r="JH1" s="10"/>
+      <c r="JI1" s="10"/>
+      <c r="JJ1" s="10"/>
+      <c r="JK1" s="10"/>
+      <c r="JL1" s="10"/>
+      <c r="JM1" s="10"/>
+      <c r="JN1" s="10"/>
+      <c r="JO1" s="10"/>
+      <c r="JP1" s="10"/>
+      <c r="JQ1" s="10"/>
+      <c r="JR1" s="10"/>
+      <c r="JS1" s="10"/>
+      <c r="JT1" s="10"/>
+      <c r="JU1" s="10"/>
+      <c r="JV1" s="10"/>
+      <c r="JW1" s="10"/>
+      <c r="JX1" s="10"/>
+      <c r="JY1" s="10"/>
+      <c r="JZ1" s="10"/>
+      <c r="KA1" s="10"/>
+      <c r="KB1" s="10"/>
+      <c r="KC1" s="10"/>
+      <c r="KD1" s="10"/>
+      <c r="KE1" s="10"/>
+      <c r="KF1" s="10"/>
+      <c r="KG1" s="10"/>
+      <c r="KH1" s="10"/>
+      <c r="KI1" s="10"/>
+      <c r="KJ1" s="10"/>
+      <c r="KK1" s="10"/>
+      <c r="KL1" s="10"/>
+      <c r="KM1" s="10"/>
+      <c r="KN1" s="10"/>
+      <c r="KO1" s="10"/>
+      <c r="KP1" s="10"/>
+      <c r="KQ1" s="10"/>
+      <c r="KR1" s="10"/>
+      <c r="KS1" s="10"/>
+      <c r="KT1" s="10"/>
+      <c r="KU1" s="10"/>
+      <c r="KV1" s="10"/>
+      <c r="KW1" s="10"/>
+      <c r="KX1" s="10"/>
+      <c r="KY1" s="10"/>
+      <c r="KZ1" s="10"/>
+      <c r="LA1" s="10"/>
+      <c r="LB1" s="10"/>
+      <c r="LC1" s="10"/>
+      <c r="LD1" s="10"/>
+      <c r="LE1" s="10"/>
+      <c r="LF1" s="10"/>
+      <c r="LG1" s="10"/>
+      <c r="LH1" s="10"/>
+      <c r="LI1" s="10"/>
+      <c r="LJ1" s="10"/>
+      <c r="LK1" s="10"/>
+      <c r="LL1" s="10"/>
+      <c r="LM1" s="10"/>
+      <c r="LN1" s="10"/>
+      <c r="LO1" s="10"/>
+      <c r="LP1" s="10"/>
+      <c r="LQ1" s="10"/>
+      <c r="LR1" s="10"/>
+      <c r="LS1" s="10"/>
+      <c r="LT1" s="10"/>
+      <c r="LU1" s="10"/>
+      <c r="LV1" s="10"/>
+      <c r="LW1" s="10"/>
+      <c r="LX1" s="10"/>
+      <c r="LY1" s="10"/>
+      <c r="LZ1" s="10"/>
+      <c r="MA1" s="10"/>
+      <c r="MB1" s="10"/>
+      <c r="MC1" s="10"/>
+      <c r="MD1" s="10"/>
+      <c r="ME1" s="10"/>
+      <c r="MF1" s="10"/>
+      <c r="MG1" s="10"/>
+      <c r="MH1" s="10"/>
+      <c r="MI1" s="10"/>
+      <c r="MJ1" s="10"/>
+      <c r="MK1" s="10"/>
+      <c r="ML1" s="10"/>
+      <c r="MM1" s="10"/>
+      <c r="MN1" s="10"/>
+      <c r="MO1" s="10"/>
+      <c r="MP1" s="10"/>
+      <c r="MQ1" s="10"/>
+      <c r="MR1" s="10"/>
+      <c r="MS1" s="10"/>
+      <c r="MT1" s="10"/>
+      <c r="MU1" s="10"/>
+      <c r="MV1" s="10"/>
+      <c r="MW1" s="10"/>
+      <c r="MX1" s="10"/>
+      <c r="MY1" s="10"/>
+      <c r="MZ1" s="10"/>
+      <c r="NA1" s="10"/>
+      <c r="NB1" s="10"/>
+      <c r="NC1" s="10"/>
+      <c r="ND1" s="10"/>
+      <c r="NE1" s="10"/>
+      <c r="NF1" s="10"/>
+      <c r="NG1" s="10"/>
+      <c r="NH1" s="10"/>
+      <c r="NI1" s="10"/>
+      <c r="NJ1" s="10"/>
+      <c r="NK1" s="10"/>
+      <c r="NL1" s="10"/>
+      <c r="NM1" s="10"/>
+      <c r="NN1" s="10"/>
+      <c r="NO1" s="10"/>
+      <c r="NP1" s="10"/>
+      <c r="NQ1" s="10"/>
+      <c r="NR1" s="10"/>
+      <c r="NS1" s="10"/>
+      <c r="NT1" s="10"/>
+      <c r="NU1" s="10"/>
+      <c r="NV1" s="10"/>
+      <c r="NW1" s="10"/>
+      <c r="NX1" s="10"/>
+      <c r="NY1" s="10"/>
+      <c r="NZ1" s="10"/>
+      <c r="OA1" s="10"/>
+      <c r="OB1" s="10"/>
+      <c r="OC1" s="10"/>
+      <c r="OD1" s="10"/>
+      <c r="OE1" s="10"/>
+      <c r="OF1" s="10"/>
+      <c r="OG1" s="10"/>
+      <c r="OH1" s="10"/>
+      <c r="OI1" s="10"/>
+      <c r="OJ1" s="10"/>
+      <c r="OK1" s="10"/>
+      <c r="OL1" s="10"/>
+      <c r="OM1" s="10"/>
+      <c r="ON1" s="10"/>
+      <c r="OO1" s="10"/>
+      <c r="OP1" s="10"/>
+      <c r="OQ1" s="10"/>
+      <c r="OR1" s="10"/>
+      <c r="OS1" s="10"/>
+      <c r="OT1" s="10"/>
+      <c r="OU1" s="10"/>
+      <c r="OV1" s="10"/>
+      <c r="OW1" s="10"/>
+      <c r="OX1" s="10"/>
+      <c r="OY1" s="10"/>
+      <c r="OZ1" s="10"/>
+      <c r="PA1" s="10"/>
+      <c r="PB1" s="10"/>
+      <c r="PC1" s="10"/>
+      <c r="PD1" s="10"/>
+      <c r="PE1" s="10"/>
+      <c r="PF1" s="10"/>
+      <c r="PG1" s="10"/>
+      <c r="PH1" s="10"/>
+      <c r="PI1" s="10"/>
+      <c r="PJ1" s="10"/>
+      <c r="PK1" s="10"/>
+      <c r="PL1" s="10"/>
+      <c r="PM1" s="10"/>
+      <c r="PN1" s="10"/>
+      <c r="PO1" s="10"/>
+      <c r="PP1" s="10"/>
+      <c r="PQ1" s="10"/>
+      <c r="PR1" s="10"/>
+      <c r="PS1" s="10"/>
+      <c r="PT1" s="10"/>
+      <c r="PU1" s="10"/>
+      <c r="PV1" s="10"/>
+      <c r="PW1" s="10"/>
+      <c r="PX1" s="10"/>
+      <c r="PY1" s="10"/>
+      <c r="PZ1" s="10"/>
+      <c r="QA1" s="10"/>
+      <c r="QB1" s="10"/>
+      <c r="QC1" s="10"/>
+      <c r="QD1" s="10"/>
+      <c r="QE1" s="10"/>
+      <c r="QF1" s="10"/>
+      <c r="QG1" s="10"/>
+      <c r="QH1" s="10"/>
+      <c r="QI1" s="10"/>
+      <c r="QJ1" s="10"/>
+      <c r="QK1" s="10"/>
+      <c r="QL1" s="10"/>
+      <c r="QM1" s="10"/>
+      <c r="QN1" s="10"/>
+      <c r="QO1" s="10"/>
+      <c r="QP1" s="10"/>
+      <c r="QQ1" s="10"/>
+      <c r="QR1" s="10"/>
+      <c r="QS1" s="10"/>
+      <c r="QT1" s="10"/>
+      <c r="QU1" s="10"/>
+      <c r="QV1" s="10"/>
+      <c r="QW1" s="10"/>
+      <c r="QX1" s="10"/>
+      <c r="QY1" s="10"/>
+      <c r="QZ1" s="10"/>
+      <c r="RA1" s="10"/>
+      <c r="RB1" s="10"/>
+      <c r="RC1" s="10"/>
+      <c r="RD1" s="10"/>
+      <c r="RE1" s="10"/>
+      <c r="RF1" s="10"/>
+      <c r="RG1" s="10"/>
+      <c r="RH1" s="10"/>
+      <c r="RI1" s="10"/>
+      <c r="RJ1" s="10"/>
+      <c r="RK1" s="10"/>
+      <c r="RL1" s="10"/>
+      <c r="RM1" s="10"/>
+      <c r="RN1" s="10"/>
+      <c r="RO1" s="10"/>
+      <c r="RP1" s="10"/>
+      <c r="RQ1" s="10"/>
+      <c r="RR1" s="10"/>
+      <c r="RS1" s="10"/>
+      <c r="RT1" s="10"/>
+      <c r="RU1" s="10"/>
+      <c r="RV1" s="10"/>
+      <c r="RW1" s="10"/>
+      <c r="RX1" s="10"/>
+      <c r="RY1" s="10"/>
+      <c r="RZ1" s="10"/>
+      <c r="SA1" s="10"/>
+      <c r="SB1" s="10"/>
+      <c r="SC1" s="10"/>
+      <c r="SD1" s="10"/>
+      <c r="SE1" s="10"/>
+      <c r="SF1" s="10"/>
+      <c r="SG1" s="10"/>
+      <c r="SH1" s="10"/>
+      <c r="SI1" s="10"/>
+      <c r="SJ1" s="10"/>
+      <c r="SK1" s="10"/>
+      <c r="SL1" s="10"/>
+      <c r="SM1" s="10"/>
+      <c r="SN1" s="10"/>
+      <c r="SO1" s="10"/>
+      <c r="SP1" s="10"/>
+      <c r="SQ1" s="10"/>
+      <c r="SR1" s="10"/>
+      <c r="SS1" s="10"/>
+      <c r="ST1" s="10"/>
+      <c r="SU1" s="10"/>
+      <c r="SV1" s="10"/>
+      <c r="SW1" s="10"/>
+      <c r="SX1" s="10"/>
+      <c r="SY1" s="10"/>
+      <c r="SZ1" s="10"/>
+      <c r="TA1" s="10"/>
+      <c r="TB1" s="10"/>
+      <c r="TC1" s="10"/>
+      <c r="TD1" s="10"/>
+      <c r="TE1" s="10"/>
+      <c r="TF1" s="10"/>
+      <c r="TG1" s="10"/>
+      <c r="TH1" s="10"/>
+      <c r="TI1" s="10"/>
+      <c r="TJ1" s="10"/>
+      <c r="TK1" s="10"/>
+      <c r="TL1" s="10"/>
+      <c r="TM1" s="10"/>
+      <c r="TN1" s="10"/>
+      <c r="TO1" s="10"/>
+      <c r="TP1" s="10"/>
+      <c r="TQ1" s="10"/>
+      <c r="TR1" s="10"/>
+      <c r="TS1" s="10"/>
+      <c r="TT1" s="10"/>
+      <c r="TU1" s="10"/>
+      <c r="TV1" s="10"/>
+      <c r="TW1" s="10"/>
+      <c r="TX1" s="10"/>
+      <c r="TY1" s="10"/>
+      <c r="TZ1" s="10"/>
+      <c r="UA1" s="10"/>
+      <c r="UB1" s="10"/>
+      <c r="UC1" s="10"/>
+      <c r="UD1" s="10"/>
+      <c r="UE1" s="10"/>
+      <c r="UF1" s="10"/>
+      <c r="UG1" s="10"/>
+      <c r="UH1" s="10"/>
+      <c r="UI1" s="10"/>
+      <c r="UJ1" s="10"/>
+      <c r="UK1" s="10"/>
+      <c r="UL1" s="10"/>
+      <c r="UM1" s="10"/>
+      <c r="UN1" s="10"/>
+      <c r="UO1" s="10"/>
+      <c r="UP1" s="10"/>
+      <c r="UQ1" s="10"/>
+      <c r="UR1" s="10"/>
+      <c r="US1" s="10"/>
+      <c r="UT1" s="10"/>
+      <c r="UU1" s="10"/>
+      <c r="UV1" s="10"/>
+      <c r="UW1" s="10"/>
+      <c r="UX1" s="10"/>
+      <c r="UY1" s="10"/>
+      <c r="UZ1" s="10"/>
+      <c r="VA1" s="10"/>
+      <c r="VB1" s="10"/>
+      <c r="VC1" s="10"/>
+      <c r="VD1" s="10"/>
+      <c r="VE1" s="10"/>
+      <c r="VF1" s="10"/>
+      <c r="VG1" s="10"/>
+      <c r="VH1" s="10"/>
+      <c r="VI1" s="10"/>
+      <c r="VJ1" s="10"/>
+      <c r="VK1" s="10"/>
+      <c r="VL1" s="10"/>
+      <c r="VM1" s="10"/>
+      <c r="VN1" s="10"/>
+      <c r="VO1" s="10"/>
+      <c r="VP1" s="10"/>
+      <c r="VQ1" s="10"/>
+      <c r="VR1" s="10"/>
+      <c r="VS1" s="10"/>
+      <c r="VT1" s="10"/>
+      <c r="VU1" s="10"/>
+      <c r="VV1" s="10"/>
+      <c r="VW1" s="10"/>
+      <c r="VX1" s="10"/>
+      <c r="VY1" s="10"/>
+      <c r="VZ1" s="10"/>
+      <c r="WA1" s="10"/>
+      <c r="WB1" s="10"/>
+      <c r="WC1" s="10"/>
+      <c r="WD1" s="10"/>
+      <c r="WE1" s="10"/>
+      <c r="WF1" s="10"/>
+      <c r="WG1" s="10"/>
+      <c r="WH1" s="10"/>
+      <c r="WI1" s="10"/>
+      <c r="WJ1" s="10"/>
+      <c r="WK1" s="10"/>
+      <c r="WL1" s="10"/>
+      <c r="WM1" s="10"/>
+      <c r="WN1" s="10"/>
+      <c r="WO1" s="10"/>
+      <c r="WP1" s="10"/>
+      <c r="WQ1" s="10"/>
+      <c r="WR1" s="10"/>
+      <c r="WS1" s="10"/>
+      <c r="WT1" s="10"/>
+      <c r="WU1" s="10"/>
+      <c r="WV1" s="10"/>
+      <c r="WW1" s="10"/>
+      <c r="WX1" s="10"/>
+      <c r="WY1" s="10"/>
+      <c r="WZ1" s="10"/>
+      <c r="XA1" s="10"/>
+      <c r="XB1" s="10"/>
+      <c r="XC1" s="10"/>
+      <c r="XD1" s="10"/>
+      <c r="XE1" s="10"/>
+      <c r="XF1" s="10"/>
+      <c r="XG1" s="10"/>
+      <c r="XH1" s="10"/>
+      <c r="XI1" s="10"/>
+      <c r="XJ1" s="10"/>
+      <c r="XK1" s="10"/>
+      <c r="XL1" s="10"/>
+      <c r="XM1" s="10"/>
+      <c r="XN1" s="10"/>
+      <c r="XO1" s="10"/>
+      <c r="XP1" s="10"/>
+      <c r="XQ1" s="10"/>
+      <c r="XR1" s="10"/>
+      <c r="XS1" s="10"/>
+      <c r="XT1" s="10"/>
+      <c r="XU1" s="10"/>
+      <c r="XV1" s="10"/>
+      <c r="XW1" s="10"/>
+      <c r="XX1" s="10"/>
+      <c r="XY1" s="10"/>
+      <c r="XZ1" s="10"/>
+      <c r="YA1" s="10"/>
+      <c r="YB1" s="10"/>
+      <c r="YC1" s="10"/>
+      <c r="YD1" s="10"/>
+      <c r="YE1" s="10"/>
+      <c r="YF1" s="10"/>
+      <c r="YG1" s="10"/>
+      <c r="YH1" s="10"/>
+      <c r="YI1" s="10"/>
+      <c r="YJ1" s="10"/>
+      <c r="YK1" s="10"/>
+      <c r="YL1" s="10"/>
+      <c r="YM1" s="10"/>
+      <c r="YN1" s="10"/>
+      <c r="YO1" s="10"/>
+      <c r="YP1" s="10"/>
+      <c r="YQ1" s="10"/>
+      <c r="YR1" s="10"/>
+      <c r="YS1" s="10"/>
+      <c r="YT1" s="10"/>
+      <c r="YU1" s="10"/>
+      <c r="YV1" s="10"/>
+      <c r="YW1" s="10"/>
+      <c r="YX1" s="10"/>
+      <c r="YY1" s="10"/>
+      <c r="YZ1" s="10"/>
+      <c r="ZA1" s="10"/>
+      <c r="ZB1" s="10"/>
+      <c r="ZC1" s="10"/>
+      <c r="ZD1" s="10"/>
+      <c r="ZE1" s="10"/>
+      <c r="ZF1" s="10"/>
+      <c r="ZG1" s="10"/>
+      <c r="ZH1" s="10"/>
+      <c r="ZI1" s="10"/>
+      <c r="ZJ1" s="10"/>
+      <c r="ZK1" s="10"/>
+      <c r="ZL1" s="10"/>
+      <c r="ZM1" s="10"/>
+      <c r="ZN1" s="10"/>
+      <c r="ZO1" s="10"/>
+      <c r="ZP1" s="10"/>
+      <c r="ZQ1" s="10"/>
+      <c r="ZR1" s="10"/>
+      <c r="ZS1" s="10"/>
+      <c r="ZT1" s="10"/>
+      <c r="ZU1" s="10"/>
+      <c r="ZV1" s="10"/>
+      <c r="ZW1" s="10"/>
+      <c r="ZX1" s="10"/>
+      <c r="ZY1" s="10"/>
+      <c r="ZZ1" s="10"/>
+      <c r="AAA1" s="10"/>
+      <c r="AAB1" s="10"/>
+      <c r="AAC1" s="10"/>
+      <c r="AAD1" s="10"/>
+      <c r="AAE1" s="10"/>
+      <c r="AAF1" s="10"/>
+      <c r="AAG1" s="10"/>
+      <c r="AAH1" s="10"/>
+      <c r="AAI1" s="10"/>
+      <c r="AAJ1" s="10"/>
+      <c r="AAK1" s="10"/>
+      <c r="AAL1" s="10"/>
+      <c r="AAM1" s="10"/>
+      <c r="AAN1" s="10"/>
+      <c r="AAO1" s="10"/>
+      <c r="AAP1" s="10"/>
+      <c r="AAQ1" s="10"/>
+      <c r="AAR1" s="10"/>
+      <c r="AAS1" s="10"/>
+      <c r="AAT1" s="10"/>
+      <c r="AAU1" s="10"/>
+      <c r="AAV1" s="10"/>
+      <c r="AAW1" s="10"/>
+      <c r="AAX1" s="10"/>
+      <c r="AAY1" s="10"/>
+      <c r="AAZ1" s="10"/>
+      <c r="ABA1" s="10"/>
+      <c r="ABB1" s="10"/>
+      <c r="ABC1" s="10"/>
+      <c r="ABD1" s="10"/>
+      <c r="ABE1" s="10"/>
+      <c r="ABF1" s="10"/>
+      <c r="ABG1" s="10"/>
+      <c r="ABH1" s="10"/>
+      <c r="ABI1" s="10"/>
+      <c r="ABJ1" s="10"/>
+      <c r="ABK1" s="10"/>
+      <c r="ABL1" s="10"/>
+      <c r="ABM1" s="10"/>
+      <c r="ABN1" s="10"/>
+      <c r="ABO1" s="10"/>
+      <c r="ABP1" s="10"/>
+      <c r="ABQ1" s="10"/>
+      <c r="ABR1" s="10"/>
+      <c r="ABS1" s="10"/>
+      <c r="ABT1" s="10"/>
+      <c r="ABU1" s="10"/>
+      <c r="ABV1" s="10"/>
+      <c r="ABW1" s="10"/>
+      <c r="ABX1" s="10"/>
+      <c r="ABY1" s="10"/>
+      <c r="ABZ1" s="10"/>
+      <c r="ACA1" s="10"/>
+      <c r="ACB1" s="10"/>
+      <c r="ACC1" s="10"/>
+      <c r="ACD1" s="10"/>
+      <c r="ACE1" s="10"/>
+      <c r="ACF1" s="10"/>
+      <c r="ACG1" s="10"/>
+      <c r="ACH1" s="10"/>
+      <c r="ACI1" s="10"/>
+      <c r="ACJ1" s="10"/>
+      <c r="ACK1" s="10"/>
+      <c r="ACL1" s="10"/>
+      <c r="ACM1" s="10"/>
+      <c r="ACN1" s="10"/>
+      <c r="ACO1" s="10"/>
+      <c r="ACP1" s="10"/>
+      <c r="ACQ1" s="10"/>
+      <c r="ACR1" s="10"/>
+      <c r="ACS1" s="10"/>
+      <c r="ACT1" s="10"/>
+      <c r="ACU1" s="10"/>
+      <c r="ACV1" s="10"/>
+      <c r="ACW1" s="10"/>
+      <c r="ACX1" s="10"/>
+      <c r="ACY1" s="10"/>
+      <c r="ACZ1" s="10"/>
+      <c r="ADA1" s="10"/>
+      <c r="ADB1" s="10"/>
+      <c r="ADC1" s="10"/>
+      <c r="ADD1" s="10"/>
+      <c r="ADE1" s="10"/>
+      <c r="ADF1" s="10"/>
+      <c r="ADG1" s="10"/>
+      <c r="ADH1" s="10"/>
+      <c r="ADI1" s="10"/>
+      <c r="ADJ1" s="10"/>
+      <c r="ADK1" s="10"/>
+      <c r="ADL1" s="10"/>
+      <c r="ADM1" s="10"/>
+      <c r="ADN1" s="10"/>
+      <c r="ADO1" s="10"/>
+      <c r="ADP1" s="10"/>
+      <c r="ADQ1" s="10"/>
+      <c r="ADR1" s="10"/>
+      <c r="ADS1" s="10"/>
+      <c r="ADT1" s="10"/>
+      <c r="ADU1" s="10"/>
+      <c r="ADV1" s="10"/>
+      <c r="ADW1" s="10"/>
+      <c r="ADX1" s="10"/>
+      <c r="ADY1" s="10"/>
+      <c r="ADZ1" s="10"/>
+      <c r="AEA1" s="10"/>
+      <c r="AEB1" s="10"/>
+      <c r="AEC1" s="10"/>
+      <c r="AED1" s="10"/>
+      <c r="AEE1" s="10"/>
+      <c r="AEF1" s="10"/>
+      <c r="AEG1" s="10"/>
+      <c r="AEH1" s="10"/>
+      <c r="AEI1" s="10"/>
+      <c r="AEJ1" s="10"/>
+      <c r="AEK1" s="10"/>
+      <c r="AEL1" s="10"/>
+      <c r="AEM1" s="10"/>
+      <c r="AEN1" s="10"/>
+      <c r="AEO1" s="10"/>
+      <c r="AEP1" s="10"/>
+      <c r="AEQ1" s="10"/>
+      <c r="AER1" s="10"/>
+      <c r="AES1" s="10"/>
+      <c r="AET1" s="10"/>
+      <c r="AEU1" s="10"/>
+      <c r="AEV1" s="10"/>
+      <c r="AEW1" s="10"/>
+      <c r="AEX1" s="10"/>
+      <c r="AEY1" s="10"/>
+      <c r="AEZ1" s="10"/>
+      <c r="AFA1" s="10"/>
+      <c r="AFB1" s="10"/>
+      <c r="AFC1" s="10"/>
+      <c r="AFD1" s="10"/>
+      <c r="AFE1" s="10"/>
+      <c r="AFF1" s="10"/>
+      <c r="AFG1" s="10"/>
+      <c r="AFH1" s="10"/>
+      <c r="AFI1" s="10"/>
+      <c r="AFJ1" s="10"/>
+      <c r="AFK1" s="10"/>
+      <c r="AFL1" s="10"/>
+      <c r="AFM1" s="10"/>
+      <c r="AFN1" s="10"/>
+      <c r="AFO1" s="10"/>
+      <c r="AFP1" s="10"/>
+      <c r="AFQ1" s="10"/>
+      <c r="AFR1" s="10"/>
+      <c r="AFS1" s="10"/>
+      <c r="AFT1" s="10"/>
+      <c r="AFU1" s="10"/>
+      <c r="AFV1" s="10"/>
+      <c r="AFW1" s="10"/>
+      <c r="AFX1" s="10"/>
+      <c r="AFY1" s="10"/>
+      <c r="AFZ1" s="10"/>
+      <c r="AGA1" s="10"/>
+      <c r="AGB1" s="10"/>
+      <c r="AGC1" s="10"/>
+      <c r="AGD1" s="11"/>
     </row>
     <row r="2" spans="1:1986">
       <c r="A2" s="1" t="s">
@@ -9066,10 +9066,10 @@
       </c>
     </row>
     <row r="3" spans="1:1986">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="12">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -9192,8 +9192,8 @@
       <c r="DL3" s="6"/>
     </row>
     <row r="4" spans="1:1986">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
@@ -9242,8 +9242,8 @@
       <c r="EZ4" s="3"/>
     </row>
     <row r="5" spans="1:1986">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
@@ -9332,8 +9332,8 @@
       <c r="IB5" s="2"/>
     </row>
     <row r="6" spans="1:1986">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
@@ -9412,8 +9412,8 @@
       <c r="KT6" s="2"/>
     </row>
     <row r="7" spans="1:1986">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
@@ -9451,8 +9451,8 @@
       <c r="LW7" s="5"/>
     </row>
     <row r="8" spans="1:1986">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
@@ -9491,8 +9491,8 @@
       <c r="NA8" s="4"/>
     </row>
     <row r="9" spans="1:1986">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
@@ -9521,8 +9521,8 @@
       <c r="NU9" s="4"/>
     </row>
     <row r="10" spans="1:1986">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
@@ -9561,10 +9561,10 @@
       <c r="OY10" s="7"/>
     </row>
     <row r="11" spans="1:1986">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="12">
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -9687,8 +9687,8 @@
       <c r="HT11" s="6"/>
     </row>
     <row r="12" spans="1:1986">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -9737,8 +9737,8 @@
       <c r="JH12" s="3"/>
     </row>
     <row r="13" spans="1:1986">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="1" t="s">
         <v>1</v>
       </c>
@@ -9827,8 +9827,8 @@
       <c r="MJ13" s="2"/>
     </row>
     <row r="14" spans="1:1986">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="1" t="s">
         <v>2</v>
       </c>
@@ -9907,8 +9907,8 @@
       <c r="QM14" s="2"/>
     </row>
     <row r="15" spans="1:1986">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="1" t="s">
         <v>9</v>
       </c>
@@ -9946,8 +9946,8 @@
       <c r="RP15" s="5"/>
     </row>
     <row r="16" spans="1:1986">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="1" t="s">
         <v>6</v>
       </c>
@@ -9986,8 +9986,8 @@
       <c r="ST16" s="4"/>
     </row>
     <row r="17" spans="1:812">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="1" t="s">
         <v>7</v>
       </c>
@@ -10016,8 +10016,8 @@
       <c r="TN17" s="4"/>
     </row>
     <row r="18" spans="1:812">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
@@ -10056,10 +10056,10 @@
       <c r="UR18" s="7"/>
     </row>
     <row r="19" spans="1:812">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="12">
         <v>3</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -10182,8 +10182,8 @@
       <c r="MB19" s="6"/>
     </row>
     <row r="20" spans="1:812">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
       <c r="C20" s="1" t="s">
         <v>8</v>
       </c>
@@ -10193,7 +10193,7 @@
       <c r="NV20" s="3"/>
       <c r="NW20" s="3"/>
       <c r="NX20" s="3"/>
-      <c r="NY20" s="14" t="s">
+      <c r="NY20" s="8" t="s">
         <v>18</v>
       </c>
       <c r="NZ20" s="3"/>
@@ -10234,8 +10234,8 @@
       <c r="PI20" s="3"/>
     </row>
     <row r="21" spans="1:812">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="1" t="s">
         <v>1</v>
       </c>
@@ -10324,8 +10324,8 @@
       <c r="SK21" s="2"/>
     </row>
     <row r="22" spans="1:812">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
@@ -10404,8 +10404,8 @@
       <c r="WF22" s="2"/>
     </row>
     <row r="23" spans="1:812">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="1" t="s">
         <v>9</v>
       </c>
@@ -10443,8 +10443,8 @@
       <c r="XI23" s="5"/>
     </row>
     <row r="24" spans="1:812">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
       <c r="C24" s="1" t="s">
         <v>6</v>
       </c>
@@ -10483,8 +10483,8 @@
       <c r="YM24" s="4"/>
     </row>
     <row r="25" spans="1:812">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
       <c r="C25" s="1" t="s">
         <v>7</v>
       </c>
@@ -10513,8 +10513,8 @@
       <c r="ZG25" s="4"/>
     </row>
     <row r="26" spans="1:812">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
@@ -10553,10 +10553,10 @@
       <c r="AAK26" s="7"/>
     </row>
     <row r="27" spans="1:812">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="12">
         <v>4</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -10679,8 +10679,8 @@
       <c r="SC27" s="6"/>
     </row>
     <row r="28" spans="1:812">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
       <c r="C28" s="1" t="s">
         <v>8</v>
       </c>
@@ -10729,8 +10729,8 @@
       <c r="VB28" s="3"/>
     </row>
     <row r="29" spans="1:812">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="1" t="s">
         <v>1</v>
       </c>
@@ -10819,8 +10819,8 @@
       <c r="YD29" s="2"/>
     </row>
     <row r="30" spans="1:812">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
@@ -10899,8 +10899,8 @@
       <c r="ABY30" s="2"/>
     </row>
     <row r="31" spans="1:812">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
       <c r="C31" s="1" t="s">
         <v>9</v>
       </c>
@@ -10938,8 +10938,8 @@
       <c r="ADB31" s="5"/>
     </row>
     <row r="32" spans="1:812">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
       <c r="C32" s="1" t="s">
         <v>6</v>
       </c>
@@ -10978,8 +10978,8 @@
       <c r="AEF32" s="4"/>
     </row>
     <row r="33" spans="1:862">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
       <c r="C33" s="1" t="s">
         <v>7</v>
       </c>
@@ -11008,8 +11008,8 @@
       <c r="AEZ33" s="4"/>
     </row>
     <row r="34" spans="1:862">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13"/>
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
